--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/62.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/62.xlsx
@@ -426,13 +426,13 @@
         <v>-21.75731152155838</v>
       </c>
       <c r="E2">
-        <v>-9.08487719125362</v>
+        <v>-19.14847780765541</v>
       </c>
       <c r="F2">
-        <v>-1.41101881525631</v>
+        <v>-3.429283805030929</v>
       </c>
       <c r="G2">
-        <v>-11.79663359803032</v>
+        <v>-15.65552300297146</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.64988169896392</v>
       </c>
       <c r="E3">
-        <v>-9.533893503010166</v>
+        <v>-20.23543836676851</v>
       </c>
       <c r="F3">
-        <v>-1.187676052848313</v>
+        <v>-3.368503175217918</v>
       </c>
       <c r="G3">
-        <v>-11.71003303726852</v>
+        <v>-15.25392899996632</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-21.37035632077168</v>
       </c>
       <c r="E4">
-        <v>-9.921675789234994</v>
+        <v>-19.90909841587975</v>
       </c>
       <c r="F4">
-        <v>-1.750101071183454</v>
+        <v>-3.302091303800676</v>
       </c>
       <c r="G4">
-        <v>-9.726182001769185</v>
+        <v>-15.45919937612883</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-20.91584967358901</v>
       </c>
       <c r="E5">
-        <v>-11.09974018843441</v>
+        <v>-20.68781933471276</v>
       </c>
       <c r="F5">
-        <v>-1.252048483719862</v>
+        <v>-3.324396752855859</v>
       </c>
       <c r="G5">
-        <v>-9.955410795999402</v>
+        <v>-14.89005535283563</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.31048767127575</v>
       </c>
       <c r="E6">
-        <v>-9.94841189977628</v>
+        <v>-20.93516458501171</v>
       </c>
       <c r="F6">
-        <v>-1.359731275879381</v>
+        <v>-3.180588858260253</v>
       </c>
       <c r="G6">
-        <v>-10.81525547836877</v>
+        <v>-14.60053490324421</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-19.5842034160687</v>
       </c>
       <c r="E7">
-        <v>-12.14223113279219</v>
+        <v>-21.57606139742127</v>
       </c>
       <c r="F7">
-        <v>-1.808888649025329</v>
+        <v>-3.502417877921889</v>
       </c>
       <c r="G7">
-        <v>-9.908291801338954</v>
+        <v>-14.28640551338662</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.79560263296306</v>
       </c>
       <c r="E8">
-        <v>-13.60920764520696</v>
+        <v>-22.42249658809096</v>
       </c>
       <c r="F8">
-        <v>-1.323508426089765</v>
+        <v>-3.318969289632716</v>
       </c>
       <c r="G8">
-        <v>-7.565610734838013</v>
+        <v>-13.44374256236607</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.99667460816088</v>
       </c>
       <c r="E9">
-        <v>-13.94661065809645</v>
+        <v>-22.78333898244416</v>
       </c>
       <c r="F9">
-        <v>-1.497037314730413</v>
+        <v>-3.211839846898267</v>
       </c>
       <c r="G9">
-        <v>-7.888064491454106</v>
+        <v>-13.10700049120248</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.25956886069135</v>
       </c>
       <c r="E10">
-        <v>-12.83603863550736</v>
+        <v>-22.9504396733272</v>
       </c>
       <c r="F10">
-        <v>-1.68634577402699</v>
+        <v>-3.115668876535453</v>
       </c>
       <c r="G10">
-        <v>-7.407244167875898</v>
+        <v>-12.77519775398349</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.6331432485064</v>
       </c>
       <c r="E11">
-        <v>-13.49547954897833</v>
+        <v>-23.5503945522334</v>
       </c>
       <c r="F11">
-        <v>-1.61216133126928</v>
+        <v>-2.884507154212431</v>
       </c>
       <c r="G11">
-        <v>-8.761945886909981</v>
+        <v>-12.77940876790944</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.17739469345909</v>
       </c>
       <c r="E12">
-        <v>-14.96610601144328</v>
+        <v>-24.75837857920149</v>
       </c>
       <c r="F12">
-        <v>-0.8367945316356927</v>
+        <v>-2.974670804170144</v>
       </c>
       <c r="G12">
-        <v>-6.390198230574239</v>
+        <v>-12.15612904868532</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.91799580007132</v>
       </c>
       <c r="E13">
-        <v>-15.65985464399636</v>
+        <v>-25.26903647915045</v>
       </c>
       <c r="F13">
-        <v>-1.329244870354151</v>
+        <v>-3.304195357003787</v>
       </c>
       <c r="G13">
-        <v>-6.494837953979522</v>
+        <v>-11.50901671212398</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.88557518398026</v>
       </c>
       <c r="E14">
-        <v>-17.75565958559024</v>
+        <v>-26.22095341488081</v>
       </c>
       <c r="F14">
-        <v>-0.5070918798104475</v>
+        <v>-3.157667103857388</v>
       </c>
       <c r="G14">
-        <v>-5.75911886605959</v>
+        <v>-11.41000491613545</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-16.07393769118984</v>
       </c>
       <c r="E15">
-        <v>-17.761415276054</v>
+        <v>-26.89518432446083</v>
       </c>
       <c r="F15">
-        <v>-0.3438480008429574</v>
+        <v>-2.52692911091558</v>
       </c>
       <c r="G15">
-        <v>-5.683277578300427</v>
+        <v>-11.12045798217972</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.47300432088179</v>
       </c>
       <c r="E16">
-        <v>-18.06461019628955</v>
+        <v>-26.92596889076497</v>
       </c>
       <c r="F16">
-        <v>-0.1376035699961448</v>
+        <v>-2.486102195101203</v>
       </c>
       <c r="G16">
-        <v>-4.946297172530032</v>
+        <v>-10.90112771911192</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-17.04385724365782</v>
       </c>
       <c r="E17">
-        <v>-18.33101126521278</v>
+        <v>-27.8055434542228</v>
       </c>
       <c r="F17">
-        <v>-0.1233846435270913</v>
+        <v>-2.262998002505213</v>
       </c>
       <c r="G17">
-        <v>-4.126526643913544</v>
+        <v>-10.58596378377331</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-17.74015173034908</v>
       </c>
       <c r="E18">
-        <v>-20.26357830425217</v>
+        <v>-27.88901681560619</v>
       </c>
       <c r="F18">
-        <v>0.7981939729050259</v>
+        <v>-1.893069829600023</v>
       </c>
       <c r="G18">
-        <v>-4.706799066036997</v>
+        <v>-10.42950409104181</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-18.50069124141252</v>
       </c>
       <c r="E19">
-        <v>-20.347903018749</v>
+        <v>-28.93511695374808</v>
       </c>
       <c r="F19">
-        <v>0.5166600571851691</v>
+        <v>-1.728594996671973</v>
       </c>
       <c r="G19">
-        <v>-5.685267216169529</v>
+        <v>-9.959658225926287</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-19.25978200671862</v>
       </c>
       <c r="E20">
-        <v>-23.64652046999422</v>
+        <v>-29.41510802771709</v>
       </c>
       <c r="F20">
-        <v>0.831862137624409</v>
+        <v>-1.628321122563093</v>
       </c>
       <c r="G20">
-        <v>-4.655250561445006</v>
+        <v>-10.17317848157266</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-19.95435218422889</v>
       </c>
       <c r="E21">
-        <v>-22.00805970385699</v>
+        <v>-29.76635911412204</v>
       </c>
       <c r="F21">
-        <v>1.590398168367916</v>
+        <v>-1.456146614626022</v>
       </c>
       <c r="G21">
-        <v>-5.362191076992054</v>
+        <v>-10.06711522358549</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-20.5232572534541</v>
       </c>
       <c r="E22">
-        <v>-24.21524246366953</v>
+        <v>-30.02433948562801</v>
       </c>
       <c r="F22">
-        <v>1.526642042844049</v>
+        <v>-1.583043388693475</v>
       </c>
       <c r="G22">
-        <v>-5.773119163145168</v>
+        <v>-9.78893339246607</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-20.92377732531216</v>
       </c>
       <c r="E23">
-        <v>-23.3403367569136</v>
+        <v>-31.18915583411798</v>
       </c>
       <c r="F23">
-        <v>1.645231120228827</v>
+        <v>-1.160613289798853</v>
       </c>
       <c r="G23">
-        <v>-5.946257384303512</v>
+        <v>-10.78594059761852</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-21.11990292470709</v>
       </c>
       <c r="E24">
-        <v>-23.56435583759905</v>
+        <v>-31.12538133466796</v>
       </c>
       <c r="F24">
-        <v>1.395345809500328</v>
+        <v>-1.252328471902009</v>
       </c>
       <c r="G24">
-        <v>-6.059425073017959</v>
+        <v>-10.39626952437307</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-21.10374255621716</v>
       </c>
       <c r="E25">
-        <v>-23.04325527658841</v>
+        <v>-30.56382565110979</v>
       </c>
       <c r="F25">
-        <v>1.334636419283958</v>
+        <v>-1.04527141263305</v>
       </c>
       <c r="G25">
-        <v>-5.967229690294795</v>
+        <v>-10.45259845672377</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-20.87425107669898</v>
       </c>
       <c r="E26">
-        <v>-23.52124476504603</v>
+        <v>-31.41763999017499</v>
       </c>
       <c r="F26">
-        <v>1.471872046905752</v>
+        <v>-1.008300547078705</v>
       </c>
       <c r="G26">
-        <v>-6.123288807016039</v>
+        <v>-10.72310644328315</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-20.45982874365942</v>
       </c>
       <c r="E27">
-        <v>-22.81325408173883</v>
+        <v>-30.6240452984638</v>
       </c>
       <c r="F27">
-        <v>1.13442664496654</v>
+        <v>-1.2341872257807</v>
       </c>
       <c r="G27">
-        <v>-5.246351778027416</v>
+        <v>-10.373039426324</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-19.88993424347862</v>
       </c>
       <c r="E28">
-        <v>-24.22604287417782</v>
+        <v>-30.83530313939563</v>
       </c>
       <c r="F28">
-        <v>1.024303482438373</v>
+        <v>-1.031220644746765</v>
       </c>
       <c r="G28">
-        <v>-5.937282495346548</v>
+        <v>-10.5980770699015</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-19.21539323562109</v>
       </c>
       <c r="E29">
-        <v>-23.39172587995265</v>
+        <v>-30.54764314924339</v>
       </c>
       <c r="F29">
-        <v>1.037179625347489</v>
+        <v>-1.165518053190829</v>
       </c>
       <c r="G29">
-        <v>-5.510870987706262</v>
+        <v>-10.445073586713</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-18.48148995575829</v>
       </c>
       <c r="E30">
-        <v>-22.82617834655672</v>
+        <v>-30.99357557020071</v>
       </c>
       <c r="F30">
-        <v>1.183015363345147</v>
+        <v>-0.9526715341437044</v>
       </c>
       <c r="G30">
-        <v>-6.941543105775541</v>
+        <v>-10.46925381133184</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-17.74346248947973</v>
       </c>
       <c r="E31">
-        <v>-21.62563460238323</v>
+        <v>-30.44570493509372</v>
       </c>
       <c r="F31">
-        <v>0.7468749555667908</v>
+        <v>-0.9798279027096806</v>
       </c>
       <c r="G31">
-        <v>-5.090931596595251</v>
+        <v>-10.71731298858943</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-17.04103321431143</v>
       </c>
       <c r="E32">
-        <v>-22.99260882328662</v>
+        <v>-30.40500980342379</v>
       </c>
       <c r="F32">
-        <v>0.7955547943597067</v>
+        <v>-1.413364751741038</v>
       </c>
       <c r="G32">
-        <v>-6.744413361094099</v>
+        <v>-11.05439273539802</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-16.41376054749491</v>
       </c>
       <c r="E33">
-        <v>-22.02567093927282</v>
+        <v>-29.61859500725176</v>
       </c>
       <c r="F33">
-        <v>0.6548226279306958</v>
+        <v>-1.595275061763213</v>
       </c>
       <c r="G33">
-        <v>-5.19313806902917</v>
+        <v>-10.5415792997283</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.87976466722996</v>
       </c>
       <c r="E34">
-        <v>-21.36748894157598</v>
+        <v>-29.52226530816059</v>
       </c>
       <c r="F34">
-        <v>0.4654934594490492</v>
+        <v>-1.555085160481589</v>
       </c>
       <c r="G34">
-        <v>-4.534465307444696</v>
+        <v>-10.50167729434346</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-15.45595890255461</v>
       </c>
       <c r="E35">
-        <v>-20.41708451616418</v>
+        <v>-29.73695573239024</v>
       </c>
       <c r="F35">
-        <v>1.442726768205654</v>
+        <v>-1.42701790327398</v>
       </c>
       <c r="G35">
-        <v>-5.219771407892607</v>
+        <v>-10.51827636967737</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-15.1376070490913</v>
       </c>
       <c r="E36">
-        <v>-19.7812505376952</v>
+        <v>-28.95345727347915</v>
       </c>
       <c r="F36">
-        <v>0.9937549493579332</v>
+        <v>-1.394127575545825</v>
       </c>
       <c r="G36">
-        <v>-3.851887096521145</v>
+        <v>-10.07213070007749</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-14.92261198994857</v>
       </c>
       <c r="E37">
-        <v>-20.84776050818967</v>
+        <v>-28.91876916258039</v>
       </c>
       <c r="F37">
-        <v>0.9644821020778043</v>
+        <v>-1.478198583255947</v>
       </c>
       <c r="G37">
-        <v>-4.894444097748428</v>
+        <v>-10.06357956094955</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-14.78924023014444</v>
       </c>
       <c r="E38">
-        <v>-19.43828203025028</v>
+        <v>-28.13399367399913</v>
       </c>
       <c r="F38">
-        <v>1.10101693087683</v>
+        <v>-1.310788844619778</v>
       </c>
       <c r="G38">
-        <v>-4.861106904167967</v>
+        <v>-9.68219147264335</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-14.72453164350957</v>
       </c>
       <c r="E39">
-        <v>-17.77345648844039</v>
+        <v>-28.10989313533031</v>
       </c>
       <c r="F39">
-        <v>0.6317683347433828</v>
+        <v>-1.320088925451008</v>
       </c>
       <c r="G39">
-        <v>-5.704623975937648</v>
+        <v>-9.496949896993431</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-14.69981507481439</v>
       </c>
       <c r="E40">
-        <v>-18.83383490512847</v>
+        <v>-27.96552538396578</v>
       </c>
       <c r="F40">
-        <v>0.6183322154699749</v>
+        <v>-1.274075601327704</v>
       </c>
       <c r="G40">
-        <v>-3.172576394044855</v>
+        <v>-10.32201398792721</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-14.7013543571742</v>
       </c>
       <c r="E41">
-        <v>-18.85495117942623</v>
+        <v>-27.24935627660073</v>
       </c>
       <c r="F41">
-        <v>0.9810030615592376</v>
+        <v>-1.498083542760149</v>
       </c>
       <c r="G41">
-        <v>-3.186252257667584</v>
+        <v>-10.04310714733469</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-14.70367434795404</v>
       </c>
       <c r="E42">
-        <v>-18.0403194617124</v>
+        <v>-26.59352002843987</v>
       </c>
       <c r="F42">
-        <v>0.5565103278316449</v>
+        <v>-1.407867705656061</v>
       </c>
       <c r="G42">
-        <v>-3.711331264560309</v>
+        <v>-10.09074589764481</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-14.70087286043401</v>
       </c>
       <c r="E43">
-        <v>-18.21866435355648</v>
+        <v>-26.73167924193988</v>
       </c>
       <c r="F43">
-        <v>0.6065950777397087</v>
+        <v>-1.203191374302748</v>
       </c>
       <c r="G43">
-        <v>-3.518478744715605</v>
+        <v>-9.776449325237479</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-14.67828693209289</v>
       </c>
       <c r="E44">
-        <v>-18.48771457977421</v>
+        <v>-25.94351192632688</v>
       </c>
       <c r="F44">
-        <v>0.4931791547854143</v>
+        <v>-1.300656254548735</v>
       </c>
       <c r="G44">
-        <v>-3.925232232943699</v>
+        <v>-9.754672556680154</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-14.64215732128052</v>
       </c>
       <c r="E45">
-        <v>-16.69139120972958</v>
+        <v>-25.83291753411156</v>
       </c>
       <c r="F45">
-        <v>0.5457374097582374</v>
+        <v>-1.395312969299231</v>
       </c>
       <c r="G45">
-        <v>-4.406032693248671</v>
+        <v>-9.705385154691484</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-14.58913437939884</v>
       </c>
       <c r="E46">
-        <v>-15.89207479110969</v>
+        <v>-24.94516907506988</v>
       </c>
       <c r="F46">
-        <v>0.3501921722859833</v>
+        <v>-1.686222347283973</v>
       </c>
       <c r="G46">
-        <v>-3.49529168375855</v>
+        <v>-9.472299574908018</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-14.53425943673613</v>
       </c>
       <c r="E47">
-        <v>-15.15104888991654</v>
+        <v>-24.60989444496399</v>
       </c>
       <c r="F47">
-        <v>0.3994286739735803</v>
+        <v>-1.355882680925975</v>
       </c>
       <c r="G47">
-        <v>-3.595223811406989</v>
+        <v>-9.733087799764105</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-14.48240335009326</v>
       </c>
       <c r="E48">
-        <v>-14.58721764816952</v>
+        <v>-24.55971442448499</v>
       </c>
       <c r="F48">
-        <v>0.7228025988414373</v>
+        <v>-1.709528464161737</v>
       </c>
       <c r="G48">
-        <v>-4.462596674332659</v>
+        <v>-9.726748105056402</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-14.45065168695403</v>
       </c>
       <c r="E49">
-        <v>-14.56144157411786</v>
+        <v>-24.08464580176232</v>
       </c>
       <c r="F49">
-        <v>0.4141669868041891</v>
+        <v>-1.553469015678727</v>
       </c>
       <c r="G49">
-        <v>-4.079311643432458</v>
+        <v>-10.02436945958242</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-14.44717502471203</v>
       </c>
       <c r="E50">
-        <v>-13.71273308949631</v>
+        <v>-23.20124920624202</v>
       </c>
       <c r="F50">
-        <v>0.214845222342572</v>
+        <v>-1.566443734308776</v>
       </c>
       <c r="G50">
-        <v>-3.81253133115029</v>
+        <v>-10.3555895407865</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-14.48365948173292</v>
       </c>
       <c r="E51">
-        <v>-13.36214768877049</v>
+        <v>-22.59948293773274</v>
       </c>
       <c r="F51">
-        <v>-0.4639090871025093</v>
+        <v>-1.465887386915541</v>
       </c>
       <c r="G51">
-        <v>-5.297473222244841</v>
+        <v>-10.45923610053</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-14.56416904513494</v>
       </c>
       <c r="E52">
-        <v>-12.70925042024061</v>
+        <v>-22.83985433805989</v>
       </c>
       <c r="F52">
-        <v>0.02499004056014773</v>
+        <v>-1.631415903179952</v>
       </c>
       <c r="G52">
-        <v>-4.981733251982391</v>
+        <v>-10.22383644941459</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-14.68902089446341</v>
       </c>
       <c r="E53">
-        <v>-12.29052959959537</v>
+        <v>-22.79887617676448</v>
       </c>
       <c r="F53">
-        <v>0.3060310776753388</v>
+        <v>-1.864653514214389</v>
       </c>
       <c r="G53">
-        <v>-5.174102432178361</v>
+        <v>-10.38966829656776</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-14.85640360644342</v>
       </c>
       <c r="E54">
-        <v>-12.11397345498432</v>
+        <v>-21.97986995315924</v>
       </c>
       <c r="F54">
-        <v>0.3787062350251478</v>
+        <v>-1.553420142001962</v>
       </c>
       <c r="G54">
-        <v>-4.767100653034822</v>
+        <v>-10.30263074379478</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-15.05742500522403</v>
       </c>
       <c r="E55">
-        <v>-10.8465215073475</v>
+        <v>-21.67271714664098</v>
       </c>
       <c r="F55">
-        <v>0.9205968538122921</v>
+        <v>-1.833783574581663</v>
       </c>
       <c r="G55">
-        <v>-5.613511141605826</v>
+        <v>-10.88072151640785</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-15.28710957780673</v>
       </c>
       <c r="E56">
-        <v>-10.68134541791773</v>
+        <v>-21.91819213717477</v>
       </c>
       <c r="F56">
-        <v>0.4405844516468681</v>
+        <v>-1.501890719343416</v>
       </c>
       <c r="G56">
-        <v>-6.296317780171587</v>
+        <v>-11.03390045850993</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-15.52974171037748</v>
       </c>
       <c r="E57">
-        <v>-12.07769132123487</v>
+        <v>-21.10236490232291</v>
       </c>
       <c r="F57">
-        <v>0.1961945302685412</v>
+        <v>-1.775539405756024</v>
       </c>
       <c r="G57">
-        <v>-5.507368430525713</v>
+        <v>-11.04578531699592</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-15.78035017501438</v>
       </c>
       <c r="E58">
-        <v>-12.23797665873636</v>
+        <v>-21.38029093759567</v>
       </c>
       <c r="F58">
-        <v>-0.2088970105180843</v>
+        <v>-1.734587406463825</v>
       </c>
       <c r="G58">
-        <v>-6.201450787198231</v>
+        <v>-11.16822253322032</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-16.02093587271249</v>
       </c>
       <c r="E59">
-        <v>-9.729052618844728</v>
+        <v>-20.51894348201871</v>
       </c>
       <c r="F59">
-        <v>0.3028252958265047</v>
+        <v>-1.766701553935556</v>
       </c>
       <c r="G59">
-        <v>-6.081979819777013</v>
+        <v>-11.46783683616098</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-16.2513475317656</v>
       </c>
       <c r="E60">
-        <v>-10.43026870503645</v>
+        <v>-20.80824051552473</v>
       </c>
       <c r="F60">
-        <v>-0.005494708230276873</v>
+        <v>-1.871534762229445</v>
       </c>
       <c r="G60">
-        <v>-6.399841849730136</v>
+        <v>-11.58711579194092</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-16.45648756735543</v>
       </c>
       <c r="E61">
-        <v>-9.17724900406208</v>
+        <v>-20.73470715458818</v>
       </c>
       <c r="F61">
-        <v>0.2307391077000861</v>
+        <v>-1.84516285759392</v>
       </c>
       <c r="G61">
-        <v>-6.828199958147514</v>
+        <v>-11.55808230756151</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-16.64208236347087</v>
       </c>
       <c r="E62">
-        <v>-9.772734279122716</v>
+        <v>-20.62979599725248</v>
       </c>
       <c r="F62">
-        <v>-0.1318074832787567</v>
+        <v>-2.008474662688439</v>
       </c>
       <c r="G62">
-        <v>-7.184305410170297</v>
+        <v>-11.83717784924977</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.79900244741968</v>
       </c>
       <c r="E63">
-        <v>-10.29164758718766</v>
+        <v>-20.18491871073894</v>
       </c>
       <c r="F63">
-        <v>-0.1756032678647665</v>
+        <v>-2.339234311319657</v>
       </c>
       <c r="G63">
-        <v>-7.187546434253243</v>
+        <v>-12.38082901661781</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-16.93736350299042</v>
       </c>
       <c r="E64">
-        <v>-10.54184577611144</v>
+        <v>-19.98965996847621</v>
       </c>
       <c r="F64">
-        <v>-0.3286640263496424</v>
+        <v>-1.800291852119076</v>
       </c>
       <c r="G64">
-        <v>-7.036228018744237</v>
+        <v>-12.53631209841522</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-17.05376227975252</v>
       </c>
       <c r="E65">
-        <v>-8.724057439270462</v>
+        <v>-19.75126751129042</v>
       </c>
       <c r="F65">
-        <v>-0.1444806761741863</v>
+        <v>-2.005983761908221</v>
       </c>
       <c r="G65">
-        <v>-6.853634879525734</v>
+        <v>-12.22182020382107</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-17.16006604249639</v>
       </c>
       <c r="E66">
-        <v>-9.514738057957722</v>
+        <v>-19.22673436698196</v>
       </c>
       <c r="F66">
-        <v>0.1936613827507803</v>
+        <v>-2.171710257981902</v>
       </c>
       <c r="G66">
-        <v>-6.940281787925079</v>
+        <v>-12.3177300186393</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-17.25424525929941</v>
       </c>
       <c r="E67">
-        <v>-8.726172236632044</v>
+        <v>-20.44798682279253</v>
       </c>
       <c r="F67">
-        <v>-0.03317377662741956</v>
+        <v>-2.310165242420616</v>
       </c>
       <c r="G67">
-        <v>-5.957053073307075</v>
+        <v>-12.32131865000387</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-17.34729127650425</v>
       </c>
       <c r="E68">
-        <v>-10.21422426707852</v>
+        <v>-18.92419154700351</v>
       </c>
       <c r="F68">
-        <v>0.01536441133961748</v>
+        <v>-1.810293560140477</v>
       </c>
       <c r="G68">
-        <v>-7.909463857819954</v>
+        <v>-12.56642151009489</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-17.43674872145925</v>
       </c>
       <c r="E69">
-        <v>-9.24333755373002</v>
+        <v>-19.95900219944428</v>
       </c>
       <c r="F69">
-        <v>-0.06480498590331868</v>
+        <v>-2.028223769938582</v>
       </c>
       <c r="G69">
-        <v>-7.308530320985909</v>
+        <v>-12.58598683423198</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-17.53135803318314</v>
       </c>
       <c r="E70">
-        <v>-10.06822173659721</v>
+        <v>-19.4621470882707</v>
       </c>
       <c r="F70">
-        <v>0.1577027821626565</v>
+        <v>-2.029788555962471</v>
       </c>
       <c r="G70">
-        <v>-7.540102981457929</v>
+        <v>-11.79004230186163</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-17.62699750952249</v>
       </c>
       <c r="E71">
-        <v>-9.900536872567189</v>
+        <v>-19.25552187624872</v>
       </c>
       <c r="F71">
-        <v>-0.268678629243319</v>
+        <v>-2.185612748103086</v>
       </c>
       <c r="G71">
-        <v>-7.06260313505561</v>
+        <v>-12.45127080460242</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-17.72993487179594</v>
       </c>
       <c r="E72">
-        <v>-10.76834646055309</v>
+        <v>-20.03683761068812</v>
       </c>
       <c r="F72">
-        <v>-0.6401442520481041</v>
+        <v>-2.022969435502625</v>
       </c>
       <c r="G72">
-        <v>-7.387668912102187</v>
+        <v>-12.75315945232856</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-17.83301614084921</v>
       </c>
       <c r="E73">
-        <v>-9.600996430855826</v>
+        <v>-19.60781451167544</v>
       </c>
       <c r="F73">
-        <v>-0.03363849074039008</v>
+        <v>-2.306756510558097</v>
       </c>
       <c r="G73">
-        <v>-6.593538558687354</v>
+        <v>-12.63129827102799</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-17.93888314978474</v>
       </c>
       <c r="E74">
-        <v>-10.59683503598658</v>
+        <v>-19.74433441758467</v>
       </c>
       <c r="F74">
-        <v>-0.651469691179179</v>
+        <v>-2.081425666383381</v>
       </c>
       <c r="G74">
-        <v>-7.572430458648912</v>
+        <v>-12.07505378842856</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-18.03619079455463</v>
       </c>
       <c r="E75">
-        <v>-10.27255554077132</v>
+        <v>-19.81260116325031</v>
       </c>
       <c r="F75">
-        <v>-0.0171722035075415</v>
+        <v>-2.046279694217403</v>
       </c>
       <c r="G75">
-        <v>-7.82885869502978</v>
+        <v>-12.79009189836467</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-18.1250033341482</v>
       </c>
       <c r="E76">
-        <v>-12.64854622616778</v>
+        <v>-20.54294439425937</v>
       </c>
       <c r="F76">
-        <v>-0.4549436667020103</v>
+        <v>-2.163797692550361</v>
       </c>
       <c r="G76">
-        <v>-7.664619220280997</v>
+        <v>-11.65096297321131</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-18.19291042598918</v>
       </c>
       <c r="E77">
-        <v>-11.93522552895356</v>
+        <v>-21.07507178947868</v>
       </c>
       <c r="F77">
-        <v>0.2620447685866851</v>
+        <v>-2.227538079093574</v>
       </c>
       <c r="G77">
-        <v>-7.590112082374159</v>
+        <v>-11.73341873095793</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-18.24281192469379</v>
       </c>
       <c r="E78">
-        <v>-11.30975722748814</v>
+        <v>-21.1271537690409</v>
       </c>
       <c r="F78">
-        <v>0.0711301048960802</v>
+        <v>-2.462487097182195</v>
       </c>
       <c r="G78">
-        <v>-7.317276782300664</v>
+        <v>-12.0028706534903</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-18.26539980294981</v>
       </c>
       <c r="E79">
-        <v>-11.73354088207394</v>
+        <v>-20.89734277009965</v>
       </c>
       <c r="F79">
-        <v>-0.7116613517687994</v>
+        <v>-2.42923560126642</v>
       </c>
       <c r="G79">
-        <v>-7.606611841341887</v>
+        <v>-11.88841847310661</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-18.2683656785887</v>
       </c>
       <c r="E80">
-        <v>-12.30508411505603</v>
+        <v>-21.86025936919464</v>
       </c>
       <c r="F80">
-        <v>-0.3009783310132773</v>
+        <v>-2.232024516947136</v>
       </c>
       <c r="G80">
-        <v>-7.564005120251466</v>
+        <v>-12.14164872249654</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-18.24626310315346</v>
       </c>
       <c r="E81">
-        <v>-11.08933375516478</v>
+        <v>-22.60503031839214</v>
       </c>
       <c r="F81">
-        <v>-0.02110860540564475</v>
+        <v>-2.602094340678204</v>
       </c>
       <c r="G81">
-        <v>-7.40214592774542</v>
+        <v>-12.11832261862684</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-18.21027786918934</v>
       </c>
       <c r="E82">
-        <v>-13.94875715477609</v>
+        <v>-23.22681697048932</v>
       </c>
       <c r="F82">
-        <v>-0.06826341981000661</v>
+        <v>-2.480111442044158</v>
       </c>
       <c r="G82">
-        <v>-6.505779306986814</v>
+        <v>-12.03641641143973</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-18.15930351617059</v>
       </c>
       <c r="E83">
-        <v>-15.31108516134761</v>
+        <v>-23.52841333940017</v>
       </c>
       <c r="F83">
-        <v>-0.3372310020293949</v>
+        <v>-2.325065086894771</v>
       </c>
       <c r="G83">
-        <v>-6.27258778974609</v>
+        <v>-11.86526782815049</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-18.10250479389945</v>
       </c>
       <c r="E84">
-        <v>-15.18339577975333</v>
+        <v>-24.63844647358235</v>
       </c>
       <c r="F84">
-        <v>-0.3616023993871592</v>
+        <v>-2.506631624444784</v>
       </c>
       <c r="G84">
-        <v>-6.777393015756319</v>
+        <v>-11.1510408018715</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-18.03932391330735</v>
       </c>
       <c r="E85">
-        <v>-17.01911687366469</v>
+        <v>-24.78636907704291</v>
       </c>
       <c r="F85">
-        <v>-0.6795612865429158</v>
+        <v>-2.521089120725843</v>
       </c>
       <c r="G85">
-        <v>-6.745790548038435</v>
+        <v>-11.39776582927677</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-17.97407494477611</v>
       </c>
       <c r="E86">
-        <v>-17.56254734000715</v>
+        <v>-26.10253381958023</v>
       </c>
       <c r="F86">
-        <v>-0.9598700468740321</v>
+        <v>-2.556911040692505</v>
       </c>
       <c r="G86">
-        <v>-6.418817896761238</v>
+        <v>-11.72441073654558</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-17.90594658480709</v>
       </c>
       <c r="E87">
-        <v>-19.08495690274982</v>
+        <v>-26.78496579558814</v>
       </c>
       <c r="F87">
-        <v>-1.054057077307141</v>
+        <v>-2.570932815719693</v>
       </c>
       <c r="G87">
-        <v>-7.361366627792678</v>
+        <v>-11.29917116202619</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-17.83461258331921</v>
       </c>
       <c r="E88">
-        <v>-19.60304602854536</v>
+        <v>-27.92662579223989</v>
       </c>
       <c r="F88">
-        <v>-1.231704608674509</v>
+        <v>-2.613606990842312</v>
       </c>
       <c r="G88">
-        <v>-6.409965497989227</v>
+        <v>-12.09791310537723</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-17.7599869132269</v>
       </c>
       <c r="E89">
-        <v>-21.87792494629856</v>
+        <v>-29.12911678023668</v>
       </c>
       <c r="F89">
-        <v>-0.9466998335369228</v>
+        <v>-2.691191881788514</v>
       </c>
       <c r="G89">
-        <v>-6.588062916365399</v>
+        <v>-11.05606787144089</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-17.67864673581643</v>
       </c>
       <c r="E90">
-        <v>-23.21618411351931</v>
+        <v>-30.71019951645972</v>
       </c>
       <c r="F90">
-        <v>-0.932907516280311</v>
+        <v>-2.687285301116911</v>
       </c>
       <c r="G90">
-        <v>-6.791502560844692</v>
+        <v>-11.44920508586596</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-17.59405825309243</v>
       </c>
       <c r="E91">
-        <v>-24.75078885676464</v>
+        <v>-32.15193205051874</v>
       </c>
       <c r="F91">
-        <v>-0.8403739071831894</v>
+        <v>-2.973568247157017</v>
       </c>
       <c r="G91">
-        <v>-6.812074290825723</v>
+        <v>-10.97035122633808</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-17.50346537015037</v>
       </c>
       <c r="E92">
-        <v>-28.5063338638578</v>
+        <v>-33.4968073182647</v>
       </c>
       <c r="F92">
-        <v>-0.4902669094921868</v>
+        <v>-2.903545522230973</v>
       </c>
       <c r="G92">
-        <v>-7.376575274000089</v>
+        <v>-11.53785487431657</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.41674086209279</v>
       </c>
       <c r="E93">
-        <v>-28.65879852674805</v>
+        <v>-35.05085506466195</v>
       </c>
       <c r="F93">
-        <v>-0.9653894588788852</v>
+        <v>-2.909836972655235</v>
       </c>
       <c r="G93">
-        <v>-7.654992153852796</v>
+        <v>-11.31236037545465</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.33167988702048</v>
       </c>
       <c r="E94">
-        <v>-28.85939633986582</v>
+        <v>-36.84864339604806</v>
       </c>
       <c r="F94">
-        <v>-0.7406972859717277</v>
+        <v>-2.735816862144726</v>
       </c>
       <c r="G94">
-        <v>-6.988311182608825</v>
+        <v>-11.4075385597087</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.26162718516984</v>
       </c>
       <c r="E95">
-        <v>-30.97096263524341</v>
+        <v>-38.42291304312657</v>
       </c>
       <c r="F95">
-        <v>-0.5085912248095146</v>
+        <v>-3.057916757947077</v>
       </c>
       <c r="G95">
-        <v>-7.063331455074249</v>
+        <v>-11.28926600977269</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.20643674234042</v>
       </c>
       <c r="E96">
-        <v>-35.43147330500665</v>
+        <v>-40.65882444204377</v>
       </c>
       <c r="F96">
-        <v>-1.059871388107391</v>
+        <v>-2.950630753773499</v>
       </c>
       <c r="G96">
-        <v>-6.279847816113713</v>
+        <v>-11.65276722053021</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.1760104460627</v>
       </c>
       <c r="E97">
-        <v>-37.51364527560045</v>
+        <v>-41.3617590841214</v>
       </c>
       <c r="F97">
-        <v>-1.208765458556186</v>
+        <v>-3.299016404001484</v>
       </c>
       <c r="G97">
-        <v>-7.380153973728041</v>
+        <v>-12.07230603563097</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-17.17171214880938</v>
       </c>
       <c r="E98">
-        <v>-40.03644003137757</v>
+        <v>-44.03164773261567</v>
       </c>
       <c r="F98">
-        <v>-1.406654975778362</v>
+        <v>-3.135237399691786</v>
       </c>
       <c r="G98">
-        <v>-7.332733719423521</v>
+        <v>-12.75401688362323</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-17.19592501235158</v>
       </c>
       <c r="E99">
-        <v>-40.86032342148907</v>
+        <v>-45.74151574114286</v>
       </c>
       <c r="F99">
-        <v>-1.087245617300304</v>
+        <v>-3.183699377857765</v>
       </c>
       <c r="G99">
-        <v>-7.052181537697984</v>
+        <v>-12.12291765583535</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-17.2543817316978</v>
       </c>
       <c r="E100">
-        <v>-42.20256991007357</v>
+        <v>-48.28276855697525</v>
       </c>
       <c r="F100">
-        <v>-1.360433731436955</v>
+        <v>-3.318556762666122</v>
       </c>
       <c r="G100">
-        <v>-8.373056102411795</v>
+        <v>-12.03311579753708</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-17.33677753422027</v>
       </c>
       <c r="E101">
-        <v>-47.37804511311582</v>
+        <v>-49.59737210809843</v>
       </c>
       <c r="F101">
-        <v>-1.527946187631071</v>
+        <v>-3.63103599945236</v>
       </c>
       <c r="G101">
-        <v>-8.169977307396282</v>
+        <v>-12.7016473637375</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-17.46609865176159</v>
       </c>
       <c r="E102">
-        <v>-49.0824155541977</v>
+        <v>-52.04663463505752</v>
       </c>
       <c r="F102">
-        <v>-1.206628270656963</v>
+        <v>-3.640185317416281</v>
       </c>
       <c r="G102">
-        <v>-7.936842069429727</v>
+        <v>-12.73131647286045</v>
       </c>
     </row>
   </sheetData>
